--- a/artfynd/A 21674-2024 artfynd.xlsx
+++ b/artfynd/A 21674-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84205318</v>
+        <v>113236856</v>
       </c>
       <c r="B2" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>sträckande V</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R2" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-07</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-07</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85169210</v>
+        <v>95896622</v>
       </c>
       <c r="B3" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,12 +824,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R3" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,22 +875,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>06:15</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>06:15</t>
+          <t>2021-08-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på fältet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +905,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maija Eloranta</t>
+          <t>Maija Eloranta, Matti  Hirvonen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -923,47 +916,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85354466</v>
+        <v>95896461</v>
       </c>
       <c r="B4" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R4" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,22 +993,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95896474</v>
+        <v>95895875</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,33 +1040,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>102987</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1099,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R5" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,27 +1106,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hela dagen.</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,53 +1134,52 @@
           <t>Maija Eloranta</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95896461</v>
+        <v>95896435</v>
       </c>
       <c r="B6" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102976</v>
+        <v>103003</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gräshoppsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Locustella naevia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1228,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R6" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1258,22 +1219,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,7 +1254,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maija Eloranta, Matti  Hirvonen</t>
+          <t>Maija Eloranta</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1304,37 +1265,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95910814</v>
+        <v>95896474</v>
       </c>
       <c r="B7" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1344,7 +1300,11 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R7" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1382,22 +1342,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>07:20</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>07:20</t>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hela dagen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,26 +1372,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maija Eloranta, Matti  Hirvonen</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Klubb Tomt 100</t>
-        </is>
-      </c>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101698986</v>
+        <v>95896659</v>
       </c>
       <c r="B8" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1467,11 +1413,7 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1480,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>635229.8626476332</v>
+        <v>635230</v>
       </c>
       <c r="R8" t="n">
-        <v>6635728.132902846</v>
+        <v>6635728</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1510,22 +1452,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vid fågelbadet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1556,49 +1493,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236856</v>
+        <v>84205318</v>
       </c>
       <c r="B9" t="n">
-        <v>56323</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100045</v>
+        <v>103037</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1638,22 +1570,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2020-04-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2020-04-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,6 +1609,480 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>85169210</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vänge-Väsby 84,Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>635230</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6635728</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>85169212</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vänge-Väsby 84,Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>635230</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6635728</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-05-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>101698960</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vänge-Väsby 84,Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>635230</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6635728</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maija Eloranta, Matti  Hirvonen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>85354466</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vänge-Väsby 84,Uppsala, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>635230</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6635728</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-05-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-05-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matti  Hirvonen, Maija Eloranta</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Klubb Tomt 100</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
